--- a/preprint/supplementary_data/Supplementary_Data_5.xlsx
+++ b/preprint/supplementary_data/Supplementary_Data_5.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>results/tables/quality/spatial_hksj.csv</t>
+          <t>results/tables/quality/spatial_hksj_assayz.csv</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>results/tables/quality/spatial_signature_overlap.csv</t>
+          <t>results/tables/quality/spatial_signature_overlap_assayz.csv</t>
         </is>
       </c>
     </row>
@@ -1115,28 +1115,28 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3924716947720277</v>
+        <v>-0.3810138214859313</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0779777269602452</v>
+        <v>0.083934174268348</v>
       </c>
       <c r="G2" t="n">
-        <v>1.046712202057749e-07</v>
+        <v>1.748826744336125e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07191248717833799</v>
+        <v>0.0834702059427327</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5272624017727849</v>
+        <v>-0.5230789745837067</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2384132410170917</v>
+        <v>-0.2183483089141858</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07797753172764529</v>
+        <v>0.08147444214569149</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002453768528526</v>
+        <v>0.0004533941781804</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7.326985414404177e-07</v>
+        <v>1.469014465242345e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002113160377141</v>
+        <v>0.0038085110967155</v>
       </c>
     </row>
     <row r="3">
@@ -1170,28 +1170,28 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2298428306831201</v>
+        <v>0.1991555488005099</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0632625330051359</v>
+        <v>0.07866193567346159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002162429100699</v>
+        <v>0.0102854152993223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0465044670875083</v>
+        <v>0.0728231521340756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08142905377730129</v>
+        <v>0.0280616491935238</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3682847983549439</v>
+        <v>0.358912577191837</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0692479793697014</v>
+        <v>0.078957394438068</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0061480075362593</v>
+        <v>0.0266853358294011</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.0007568501852448</v>
+        <v>0.0269992151607212</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0215180263769078</v>
+        <v>0.0622657836019359</v>
       </c>
     </row>
     <row r="4">
@@ -1225,28 +1225,28 @@
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2671604038121419</v>
+        <v>-0.2699169578636075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0703011539322639</v>
+        <v>0.0655071582165566</v>
       </c>
       <c r="G4" t="n">
-        <v>9.83113420824362e-05</v>
+        <v>2.388353663101763e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0580462640642917</v>
+        <v>0.0502206261244434</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3855721576848643</v>
+        <v>-0.3750114810184226</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1400910566712349</v>
+        <v>-0.1579723516159004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.060329806787471</v>
+        <v>0.0533705493424351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008460220070343</v>
+        <v>0.0003009848090118</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.0003753705788602</v>
+        <v>0.0001003108538502</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0050761320422059</v>
+        <v>0.003160340494624</v>
       </c>
     </row>
     <row r="5">
@@ -1280,28 +1280,28 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0071996510085152</v>
+        <v>-0.0286828524861759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0660984904046827</v>
+        <v>0.0663491770483611</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9132620093710599</v>
+        <v>0.6654360632945617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0511368284941424</v>
+        <v>0.0514771980791485</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1381214712460683</v>
+        <v>-0.157998159969409</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1239694598028954</v>
+        <v>0.101599721270588</v>
       </c>
       <c r="K5" t="n">
-        <v>0.059886922711659</v>
+        <v>0.0593562441721093</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9064743992137992</v>
+        <v>0.6383145037425376</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.9355366925264512</v>
+        <v>0.7228152274661102</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9285835309019408</v>
+        <v>0.7245732204645021</v>
       </c>
     </row>
     <row r="6">
@@ -1335,28 +1335,28 @@
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1285697713181599</v>
+        <v>0.1267586977714778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.057008939481083</v>
+        <v>0.0600275851061029</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0233409329818846</v>
+        <v>0.0337459436541682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0376716887110108</v>
+        <v>0.0420029357528133</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0055206610156699</v>
+        <v>-0.0184991056116509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2581182980661897</v>
+        <v>0.2667761054511844</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0612480395528102</v>
+        <v>0.0663091454074156</v>
       </c>
       <c r="L6" t="n">
-        <v>0.058490816340214</v>
+        <v>0.08088182607563769</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.0484687305433607</v>
+        <v>0.06749188730833661</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1169816326804281</v>
+        <v>0.1544107588716719</v>
       </c>
     </row>
     <row r="7">
@@ -1390,28 +1390,28 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3060010213223723</v>
+        <v>-0.3203991561765821</v>
       </c>
       <c r="F7" t="n">
-        <v>0.076388556785512</v>
+        <v>0.0671616688818132</v>
       </c>
       <c r="G7" t="n">
-        <v>3.497183284571755e-05</v>
+        <v>7.627543189858468e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0688694397071679</v>
+        <v>0.0529639939636613</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4559855652936009</v>
+        <v>-0.459650781588779</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1391153323927403</v>
+        <v>-0.1657712869712978</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0800114278952638</v>
+        <v>0.0748649151769443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0022686972884912</v>
+        <v>0.0010018189819158</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.0001632018866133</v>
+        <v>1.06785604658019e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0086622987378756</v>
+        <v>0.0053111528914532</v>
       </c>
     </row>
     <row r="8">
@@ -1445,28 +1445,28 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0415802881815799</v>
+        <v>-0.0755855117489391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07608695469258819</v>
+        <v>0.0768381573101222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5845167820180266</v>
+        <v>0.3243405315844138</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0684327516041152</v>
+        <v>0.0698088947684143</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2561134115239106</v>
+        <v>-0.2915273881498942</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1768566520730997</v>
+        <v>0.1476867797287085</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1001098295041298</v>
+        <v>0.1020019403357618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6857043047365498</v>
+        <v>0.4733794096821801</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.6768941714982009</v>
+        <v>0.4256969477045426</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7652755323000414</v>
+        <v>0.5680552916186161</v>
       </c>
     </row>
     <row r="9">
@@ -1500,28 +1500,28 @@
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1755475058632371</v>
+        <v>0.1730667594388838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1152224255683819</v>
+        <v>0.1164768554464122</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1236823735771404</v>
+        <v>0.1333674715663392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1578216696173729</v>
+        <v>0.1611444705459552</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08351563073272709</v>
+        <v>-0.0744079794771389</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4123840365774649</v>
+        <v>0.4004615808631302</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1186266500333526</v>
+        <v>0.1133002438382328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.162956715908099</v>
+        <v>0.1510854776474271</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.1997946034707653</v>
+        <v>0.2333930752410935</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2632377718515445</v>
+        <v>0.2538236024476775</v>
       </c>
     </row>
     <row r="10">
@@ -1555,28 +1555,28 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.238334316401219</v>
+        <v>0.2235963282932129</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0860408026756366</v>
+        <v>0.0818333283998485</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0047380006358821</v>
+        <v>0.0054477938644506</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08768360039034601</v>
+        <v>0.0791576671993396</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0699521487825383</v>
+        <v>0.0664352126922868</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3935114899642985</v>
+        <v>0.3699315703249453</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0785742622651289</v>
+        <v>0.0731060371552536</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0102364473978874</v>
+        <v>0.0099064139805878</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.0124372516691907</v>
+        <v>0.0152538228204619</v>
       </c>
       <c r="O10" t="n">
-        <v>0.031444939170754</v>
+        <v>0.0346724489320574</v>
       </c>
     </row>
     <row r="11">
@@ -1610,28 +1610,28 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1827974785859264</v>
+        <v>-0.1638779798522556</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0813333467162064</v>
+        <v>0.077717335230375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0230227297897987</v>
+        <v>0.0333513517628321</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0781048556041537</v>
+        <v>0.071182566148833</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3218540193718722</v>
+        <v>-0.2957269284811363</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0360211089533604</v>
+        <v>-0.0259019476022129</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06762365152150721</v>
+        <v>0.0633631600211871</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0194428058221556</v>
+        <v>0.0242634703879133</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.0484687305433607</v>
+        <v>0.06749188730833661</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0492238900979471</v>
+        <v>0.0599450444877858</v>
       </c>
     </row>
     <row r="12">
@@ -1665,28 +1665,28 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2070809396558491</v>
+        <v>-0.2045691639171849</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09348675080461161</v>
+        <v>0.0876790683898508</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0246025655996458</v>
+        <v>0.0179548752277697</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1033180877555485</v>
+        <v>0.09076408941944331</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4096705098327559</v>
+        <v>-0.4008408448858984</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0149749699299275</v>
+        <v>0.0096566954931981</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1022704095654848</v>
+        <v>0.09866203118116031</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06446837498013221</v>
+        <v>0.0592806751515324</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.0484687305433607</v>
+        <v>0.041894708864796</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1177248586593718</v>
+        <v>0.1185613503030649</v>
       </c>
     </row>
     <row r="13">
@@ -1720,28 +1720,28 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2108665334412703</v>
+        <v>0.2041240482290595</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0957654389718699</v>
+        <v>0.089449972412357</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0253883826655699</v>
+        <v>0.0206401905442332</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1087392736275844</v>
+        <v>0.0946795709810009</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0021632949341534</v>
+        <v>0.0151613614812118</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4019669707114439</v>
+        <v>0.3790089019589214</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0962817630516306</v>
+        <v>0.0871744336840999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0480740310580834</v>
+        <v>0.0368304098243197</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.0484687305433607</v>
+        <v>0.0456256843609366</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1009554652219751</v>
+        <v>0.08141459013796989</v>
       </c>
     </row>
     <row r="14">
@@ -1775,28 +1775,28 @@
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04359897044336</v>
+        <v>-0.0482822757344439</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1003327338586373</v>
+        <v>0.1145475168598121</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6636934629326078</v>
+        <v>0.6731474022928143</v>
       </c>
       <c r="H14" t="n">
-        <v>0.11974029755037</v>
+        <v>0.1563916180426603</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2729249779537718</v>
+        <v>-0.293797671792595</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1904154789489102</v>
+        <v>0.2032094389079683</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1074041186792939</v>
+        <v>0.1155836122921</v>
       </c>
       <c r="L14" t="n">
-        <v>0.692392148271466</v>
+        <v>0.6839544142598276</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.7335559327149876</v>
+        <v>0.7228152274661102</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7652755323000414</v>
+        <v>0.7365662922798143</v>
       </c>
     </row>
     <row r="15">
@@ -1830,28 +1830,28 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2447318131009175</v>
+        <v>-0.2475333710572116</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08286494803943779</v>
+        <v>0.0828008483441373</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0025735353948595</v>
+        <v>0.0022663456858786</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0807438954193142</v>
+        <v>0.0806147686728228</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.426399904193814</v>
+        <v>-0.4187071844587304</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.044085608305203</v>
+        <v>-0.0593736687463222</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09345225870002449</v>
+        <v>0.08784242738229391</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0216761584442253</v>
+        <v>0.0150332230116771</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.0072058991056068</v>
+        <v>0.0079322099005754</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0505777030365257</v>
+        <v>0.0450996690350315</v>
       </c>
     </row>
     <row r="16">
@@ -1885,28 +1885,28 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.288979768370453</v>
+        <v>-0.3033927935275901</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0535126394013333</v>
+        <v>0.0416487675755464</v>
       </c>
       <c r="G16" t="n">
-        <v>2.720241738317855e-08</v>
+        <v>5.424156158615718e-14</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0332709481439729</v>
+        <v>0.0197228501066349</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3930070884777086</v>
+        <v>-0.3879967639658028</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.177648927380968</v>
+        <v>-0.2137185612213777</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0535663599506609</v>
+        <v>0.0437020115272836</v>
       </c>
       <c r="L16" t="n">
-        <v>0.000171989566099</v>
+        <v>1.826185264210813e-05</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.808338433644982e-07</v>
+        <v>2.278145586618602e-12</v>
       </c>
       <c r="O16" t="n">
-        <v>0.002113160377141</v>
+        <v>0.0007669978109685</v>
       </c>
     </row>
     <row r="17">
@@ -1940,28 +1940,28 @@
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0570485579175275</v>
+        <v>-0.0712801377465159</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1078143467429259</v>
+        <v>0.1076596458507126</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5963115320341293</v>
+        <v>0.507194433264583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1382807937833587</v>
+        <v>0.1378915450189917</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2528675119794895</v>
+        <v>-0.2635378864515788</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1432603871345132</v>
+        <v>0.1264240217986571</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0914877924935905</v>
+        <v>0.0901893089673422</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5451972604321027</v>
+        <v>0.4452827209604253</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.6768941714982009</v>
+        <v>0.5917268388086803</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6360634705041198</v>
+        <v>0.5643029923962924</v>
       </c>
     </row>
     <row r="18">
@@ -1995,28 +1995,28 @@
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1475199965836814</v>
+        <v>0.1364407797016483</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1096756672941169</v>
+        <v>0.1055271770564703</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1754356307870649</v>
+        <v>0.1932384378938716</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1430899110437912</v>
+        <v>0.1323957225612299</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.110713118424418</v>
+        <v>-0.1131897316951788</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3870941160398994</v>
+        <v>0.3698686564442485</v>
       </c>
       <c r="K18" t="n">
-        <v>0.118025845222427</v>
+        <v>0.1140279851128658</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2340634668970079</v>
+        <v>0.2538345215331712</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.2540791894157492</v>
+        <v>0.2798625652256072</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3389884692991149</v>
+        <v>0.367622410496317</v>
       </c>
     </row>
     <row r="19">
@@ -2050,28 +2050,28 @@
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4410446486904676</v>
+        <v>-0.4034367717389327</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0706136909756266</v>
+        <v>0.07311285020698829</v>
       </c>
       <c r="G19" t="n">
-        <v>2.001951595084676e-11</v>
+        <v>4.900843764558833e-09</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0587610178621979</v>
+        <v>0.063038806476443</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.564253279326062</v>
+        <v>-0.5384965393130943</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2986189316573585</v>
+        <v>-0.2481668580373075</v>
       </c>
       <c r="K19" t="n">
-        <v>0.075204666557238</v>
+        <v>0.0791866499845698</v>
       </c>
       <c r="L19" t="n">
-        <v>5.865916062543274e-05</v>
+        <v>0.0002160818856928</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>8.408196699355641e-10</v>
+        <v>1.029177190557377e-07</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0019293228393244</v>
+        <v>0.0030251463997001</v>
       </c>
     </row>
     <row r="20">
@@ -2105,28 +2105,28 @@
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1203487158694839</v>
+        <v>-0.0520233981093001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1034870925793164</v>
+        <v>0.1234110169620044</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2425654600218569</v>
+        <v>0.673078497241795</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1274714564674965</v>
+        <v>0.1817171429042154</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.350938694710669</v>
+        <v>-0.3325889233442374</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1240026730287479</v>
+        <v>0.2370022442488249</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1115768716542697</v>
+        <v>0.1334247775892864</v>
       </c>
       <c r="L20" t="n">
-        <v>0.301607426704673</v>
+        <v>0.7037952600890205</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.3286370748683223</v>
+        <v>0.7228152274661102</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3958597475498834</v>
+        <v>0.7389850230934716</v>
       </c>
     </row>
     <row r="21">
@@ -2160,28 +2160,28 @@
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3541239889823535</v>
+        <v>-0.331524059250812</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06767975241839259</v>
+        <v>0.0797902807090614</v>
       </c>
       <c r="G21" t="n">
-        <v>4.521794520208742e-08</v>
+        <v>1.574038329974165e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0536682154965195</v>
+        <v>0.07512530458874229</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5068479439978708</v>
+        <v>-0.4955006361607776</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1798460625106378</v>
+        <v>-0.1447307540533621</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0855651538132569</v>
+        <v>0.09031652358639169</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0012026474996638</v>
+        <v>0.0028688310300008</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.74788424621918e-07</v>
+        <v>8.263701232364318e-05</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0056123549984314</v>
+        <v>0.0120490903260035</v>
       </c>
     </row>
     <row r="22">
@@ -2215,28 +2215,28 @@
         <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2376585731098313</v>
+        <v>-0.2406796318507436</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0528021480425859</v>
+        <v>0.0578204675355209</v>
       </c>
       <c r="G22" t="n">
-        <v>4.461024500601651e-06</v>
+        <v>2.177935543450123e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0322758197331115</v>
+        <v>0.0389473962977684</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3425735925452476</v>
+        <v>-0.3521767044093731</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1268890361332801</v>
+        <v>-0.122446806091081</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0521195491492257</v>
+        <v>0.0556255821172808</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0007065103078624</v>
+        <v>0.001039905900453</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.342037862815859e-05</v>
+        <v>0.0001003108538502</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004945572155037</v>
+        <v>0.0053111528914532</v>
       </c>
     </row>
     <row r="23">
@@ -2270,28 +2270,28 @@
         <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0198461347195582</v>
+        <v>-0.0610519582806789</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0854482906875513</v>
+        <v>0.0911170413709842</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8163131653152103</v>
+        <v>0.5023013029048307</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0862728194627162</v>
+        <v>0.09829984076607221</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2061268469259122</v>
+        <v>-0.255529701511095</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1678227298467836</v>
+        <v>0.1381744125530243</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0859952136399086</v>
+        <v>0.0909556142233942</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8216974707164623</v>
+        <v>0.5154107069615725</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.8791064857240726</v>
+        <v>0.5917268388086803</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8627823442522854</v>
+        <v>0.601312491455168</v>
       </c>
     </row>
     <row r="24">
@@ -2325,28 +2325,28 @@
         <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0071313256883872</v>
+        <v>0.0018277945997265</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0908568248783848</v>
+        <v>0.0945737165000802</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9374374581017072</v>
+        <v>0.9845804946034534</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0979180709169318</v>
+        <v>0.1061955013595108</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2064767658955265</v>
+        <v>-0.221522932976927</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2200905788362384</v>
+        <v>0.2249963092718748</v>
       </c>
       <c r="K24" t="n">
-        <v>0.09841949604739771</v>
+        <v>0.1031741907051025</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9435368212393114</v>
+        <v>0.9861829535496224</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.9374374581017076</v>
+        <v>0.9845804946034536</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9435368212393114</v>
+        <v>0.9861829535496224</v>
       </c>
     </row>
     <row r="25">
@@ -2380,28 +2380,28 @@
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3652632573023997</v>
+        <v>-0.3593374522742528</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0819314462150293</v>
+        <v>0.08470800950278499</v>
       </c>
       <c r="G25" t="n">
-        <v>2.954151700053811e-06</v>
+        <v>8.985358923902245e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0794012894672385</v>
+        <v>0.08493896825724449</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5180385765882762</v>
+        <v>-0.5124446009392533</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1899035125539145</v>
+        <v>-0.1840876966906825</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0866471259949613</v>
+        <v>0.0862860923998657</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0010291872524132</v>
+        <v>0.0011381041910256</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.772491020032296e-05</v>
+        <v>5.391215354341347e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0054032330751697</v>
+        <v>0.0053111528914532</v>
       </c>
     </row>
     <row r="26">
@@ -2435,28 +2435,28 @@
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1276995601070703</v>
+        <v>-0.1066719237153896</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0561867642064173</v>
+        <v>0.0579361586947377</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0222984140387629</v>
+        <v>0.06456916417406069</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0368675538100842</v>
+        <v>0.0392649845867329</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2402580492674168</v>
+        <v>-0.2381206788285023</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0117526502319053</v>
+        <v>0.0286144406325048</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0529978040932666</v>
+        <v>0.0616549208925194</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0338414697051951</v>
+        <v>0.1103132061056117</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.0484687305433607</v>
+        <v>0.1203776067422611</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0748074593483261</v>
+        <v>0.2014415068015518</v>
       </c>
     </row>
     <row r="27">
@@ -2490,28 +2490,28 @@
         <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2415331919956099</v>
+        <v>-0.2335705880653234</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0440145864746994</v>
+        <v>0.0491048544694511</v>
       </c>
       <c r="G27" t="n">
-        <v>2.166117023335311e-08</v>
+        <v>1.259670637201624e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0220711399132404</v>
+        <v>0.0277163811670813</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3352090410176253</v>
+        <v>-0.3342567787471967</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1431284948177348</v>
+        <v>-0.1276131507395929</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0464717348553794</v>
+        <v>0.0498186220698939</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0002515667115644</v>
+        <v>0.000574562800498</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.808338433644982e-07</v>
+        <v>1.322654169061705e-05</v>
       </c>
       <c r="O27" t="n">
-        <v>0.002113160377141</v>
+        <v>0.0040219396034865</v>
       </c>
     </row>
     <row r="28">
@@ -2545,28 +2545,28 @@
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.09657293983555661</v>
+        <v>-0.1081023641182549</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0315387981037185</v>
+        <v>0.0382256052363771</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0021290844123031</v>
+        <v>0.0045240513308635</v>
       </c>
       <c r="H28" t="n">
-        <v>0.010942745230976</v>
+        <v>0.0165158870735517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1733458806195704</v>
+        <v>-0.1943440207594385</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0186334021176776</v>
+        <v>-0.0202023571018445</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0355473981439279</v>
+        <v>0.0401280917753882</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0197459759558335</v>
+        <v>0.0204912904819901</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.0063872532369093</v>
+        <v>0.0146161658381744</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0492238900979471</v>
+        <v>0.0573756133495725</v>
       </c>
     </row>
     <row r="29">
@@ -2600,28 +2600,28 @@
         <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0655918298202874</v>
+        <v>-0.0763107120024084</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0524478973458804</v>
+        <v>0.0518229855637963</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2104214261024855</v>
+        <v>0.1401064551137254</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0318492250215243</v>
+        <v>0.0310572724363125</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.185094050199871</v>
+        <v>-0.1923659740778856</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0558219874767902</v>
+        <v>0.0418497282960684</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0552326380438032</v>
+        <v>0.0537638994983228</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2593742997980974</v>
+        <v>0.1827185695878047</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.2945899965434798</v>
+        <v>0.2353788445910591</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3631240197173363</v>
+        <v>0.2842288860254741</v>
       </c>
     </row>
     <row r="30">
@@ -2655,28 +2655,28 @@
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0609168801262541</v>
+        <v>-0.055409839994944</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0650166597490202</v>
+        <v>0.0660239415615336</v>
       </c>
       <c r="G30" t="n">
-        <v>0.348190877633896</v>
+        <v>0.4008528402779953</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0496407794116387</v>
+        <v>0.0512120617663503</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2062316151498073</v>
+        <v>-0.2105630922687572</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0870268419661861</v>
+        <v>0.1024662999059702</v>
       </c>
       <c r="K30" t="n">
-        <v>0.06735163530699451</v>
+        <v>0.0719195388510413</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3845638046565949</v>
+        <v>0.4568167081303319</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.4301181429595186</v>
+        <v>0.4951711556375236</v>
       </c>
       <c r="O30" t="n">
-        <v>0.4750494057522643</v>
+        <v>0.5643029923962924</v>
       </c>
     </row>
     <row r="31">
@@ -2710,28 +2710,28 @@
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1919496516745583</v>
+        <v>-0.1888973276542394</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0528317668596443</v>
+        <v>0.0564195541351561</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0002342797629047</v>
+        <v>0.0007020435270276</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0324560931922093</v>
+        <v>0.0371318968772046</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3214619957424552</v>
+        <v>-0.3250223713135842</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0553877526181789</v>
+        <v>-0.0451037350654633</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0631154291783222</v>
+        <v>0.0663607789415341</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0104816463902513</v>
+        <v>0.0149412865551833</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.0007569038493845</v>
+        <v>0.002680529830469</v>
       </c>
       <c r="O31" t="n">
-        <v>0.031444939170754</v>
+        <v>0.0450996690350315</v>
       </c>
     </row>
     <row r="32">
@@ -2765,28 +2765,28 @@
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.093761640953826</v>
+        <v>0.0755168906526353</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0663921896577673</v>
+        <v>0.0644752126230229</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1566585891797172</v>
+        <v>0.2405998670392148</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0518418257483102</v>
+        <v>0.0488308983520548</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0675340558556148</v>
+        <v>-0.07056122791568489</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2502811507220011</v>
+        <v>0.2184240044579241</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0734556831523667</v>
+        <v>0.0664882360663045</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2268132394023079</v>
+        <v>0.2793161733263755</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.2436911387240045</v>
+        <v>0.3368398138549009</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3389884692991149</v>
+        <v>0.3784283638615409</v>
       </c>
     </row>
     <row r="33">
@@ -2820,28 +2820,28 @@
         <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.06443163933574279</v>
+        <v>-0.0605465753007571</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0470687053613386</v>
+        <v>0.0428521592372106</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1704423321969865</v>
+        <v>0.157171708937292</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0254593129842851</v>
+        <v>0.0208782216218495</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1711248957576804</v>
+        <v>-0.1655339546121924</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0437552625711398</v>
+        <v>0.045797760863463</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0492071657293344</v>
+        <v>0.0483649533559919</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2164969654938802</v>
+        <v>0.2360457026313123</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.2540791894157492</v>
+        <v>0.2538927605910107</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3367730574349249</v>
+        <v>0.3540685539469685</v>
       </c>
     </row>
     <row r="34">
@@ -2875,28 +2875,28 @@
         <v>12</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0141243510186505</v>
+        <v>-0.0062213950557557</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0792275881078691</v>
+        <v>0.0775275758294748</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8584971775276646</v>
+        <v>0.9360395795775652</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07418891634706259</v>
+        <v>0.07097468686971919</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1388369864349122</v>
+        <v>-0.1272290174655671</v>
       </c>
       <c r="J34" t="n">
-        <v>0.111029284890496</v>
+        <v>0.1149687070146708</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0570718149474729</v>
+        <v>0.0552937769456372</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8090800149481108</v>
+        <v>0.9124407729797552</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.9014220364040481</v>
+        <v>0.9588698132257985</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8627823442522854</v>
+        <v>0.9346954259792616</v>
       </c>
     </row>
     <row r="35">
@@ -2930,28 +2930,28 @@
         <v>12</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1044299071417225</v>
+        <v>-0.0691396649329121</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0581290496621329</v>
+        <v>0.0526190003118343</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0713737401964049</v>
+        <v>0.1881514193046587</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0393996351242863</v>
+        <v>0.0320479457205364</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2233144623189175</v>
+        <v>-0.1729587541276898</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0175159750499698</v>
+        <v>0.0361989324507284</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0555795665580302</v>
+        <v>0.0479171369902292</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0859902590163608</v>
+        <v>0.1762792770962435</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0.1249040453437087</v>
+        <v>0.2798625652256072</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1444636351474862</v>
+        <v>0.2842288860254741</v>
       </c>
     </row>
     <row r="36">
@@ -2985,28 +2985,28 @@
         <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.1050658190473382</v>
+        <v>-0.0966076059389821</v>
       </c>
       <c r="F36" t="n">
-        <v>0.055708315002521</v>
+        <v>0.0526981814282112</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0583598728213515</v>
+        <v>0.0659210703588573</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0360312451987834</v>
+        <v>0.0320124592752965</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2145662632432868</v>
+        <v>-0.1928871741646527</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0070429868336511</v>
+        <v>0.0015144923935153</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0511126137627506</v>
+        <v>0.0447183119628876</v>
       </c>
       <c r="L36" t="n">
-        <v>0.06351503640320739</v>
+        <v>0.0530427685305941</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.1065702025433375</v>
+        <v>0.1203776067422611</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1177248586593718</v>
+        <v>0.1113898139142476</v>
       </c>
     </row>
     <row r="37">
@@ -3040,28 +3040,28 @@
         <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1605421389800861</v>
+        <v>-0.1264879830890674</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0937931099879724</v>
+        <v>0.09193714701221301</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08423963250609511</v>
+        <v>0.1665980780816207</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1044631442500201</v>
+        <v>0.1002833884242094</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3269098861543237</v>
+        <v>-0.298838199527322</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0154769602078222</v>
+        <v>0.0538530314511011</v>
       </c>
       <c r="K37" t="n">
-        <v>0.08060995933046371</v>
+        <v>0.0822696531306783</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0697233883022513</v>
+        <v>0.1504311800071117</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.1415225826102398</v>
+        <v>0.2591525659047435</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1220159295289397</v>
+        <v>0.2538236024476775</v>
       </c>
     </row>
     <row r="38">
@@ -3095,28 +3095,28 @@
         <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0904566669900962</v>
+        <v>-0.0413415183220678</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08836343072512801</v>
+        <v>0.1031462317740034</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3046584080362817</v>
+        <v>0.6883954547296287</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0926262434258389</v>
+        <v>0.1265852885741177</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2728022495262326</v>
+        <v>-0.243355431969351</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09816256112473611</v>
+        <v>0.1641099518724</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0859543706801708</v>
+        <v>0.0940363430811849</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3139308480396603</v>
+        <v>0.6685387630678808</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.3877470647734499</v>
+        <v>0.7228152274661102</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3995483520504768</v>
+        <v>0.7365662922798143</v>
       </c>
     </row>
     <row r="39">
@@ -3150,28 +3150,28 @@
         <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1427101424114592</v>
+        <v>0.1443229232393491</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0521266850050977</v>
+        <v>0.0588380280967784</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0058410696172864</v>
+        <v>0.0135063340496385</v>
       </c>
       <c r="H39" t="n">
-        <v>0.031349990708936</v>
+        <v>0.0402478883277387</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0274204127359396</v>
+        <v>0.0254297631678028</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2542531286474786</v>
+        <v>0.2591902104815734</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0528234767226566</v>
+        <v>0.0544767089014276</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0199239555158357</v>
+        <v>0.0218764266759815</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.0144308778780017</v>
+        <v>0.0333685900049894</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0492238900979471</v>
+        <v>0.0574256200244515</v>
       </c>
     </row>
     <row r="40">
@@ -3205,28 +3205,28 @@
         <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.2235283753465725</v>
+        <v>-0.1717498707120491</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0554622076136927</v>
+        <v>0.0616311278069926</v>
       </c>
       <c r="G40" t="n">
-        <v>4.140543944371163e-05</v>
+        <v>0.0048832575582101</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0357386321441308</v>
+        <v>0.0444398331124007</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3374255348688516</v>
+        <v>-0.2748859391420311</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1031810268009192</v>
+        <v>-0.0647062821902971</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0562554622907119</v>
+        <v>0.0493744122054915</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0019428833284681</v>
+        <v>0.0048549772617757</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.0001739028456635</v>
+        <v>0.0146497726746303</v>
       </c>
       <c r="O40" t="n">
-        <v>0.008160109979566199</v>
+        <v>0.0185371859085982</v>
       </c>
     </row>
     <row r="41">
@@ -3260,28 +3260,28 @@
         <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.06653884206936921</v>
+        <v>-0.07452622694878119</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0630913710173444</v>
+        <v>0.07277786035487741</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2908754310550879</v>
+        <v>0.3049266847600078</v>
       </c>
       <c r="H41" t="n">
-        <v>0.046550512181545</v>
+        <v>0.0623211097816127</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1989656308628024</v>
+        <v>-0.2144865967741626</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0682743315963445</v>
+        <v>0.0684331374812558</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0613443553386553</v>
+        <v>0.0650640144897903</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3005852179326692</v>
+        <v>0.2754975445718196</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.3817740032598032</v>
+        <v>0.4131264761264623</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3958597475498834</v>
+        <v>0.3784283638615409</v>
       </c>
     </row>
     <row r="42">
@@ -3315,28 +3315,28 @@
         <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0486666632725363</v>
+        <v>-0.0587179084357666</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05867677080868</v>
+        <v>0.0658758546973946</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4065058342093505</v>
+        <v>0.3721955051739465</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0400037500276681</v>
+        <v>0.0507002248468415</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.175431502792496</v>
+        <v>-0.1734218364331092</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0796856031694587</v>
+        <v>0.0575577116694027</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0584102304846686</v>
+        <v>0.0528885573548268</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4221058209818905</v>
+        <v>0.2900573846434898</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.4878070010512207</v>
+        <v>0.4737033702213863</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5065269851782687</v>
+        <v>0.3807003173445804</v>
       </c>
     </row>
     <row r="43">
@@ -3370,28 +3370,28 @@
         <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.3461537054154968</v>
+        <v>-0.2864979404986337</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0665959089501526</v>
+        <v>0.06484322656261329</v>
       </c>
       <c r="G43" t="n">
-        <v>5.901427081746225e-08</v>
+        <v>5.479710254087475e-06</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0520249627101242</v>
+        <v>0.0492279141412565</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.4573554112033252</v>
+        <v>-0.3898606465671327</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2242933401546702</v>
+        <v>-0.1760060219432328</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0603797209002067</v>
+        <v>0.0531075093706376</v>
       </c>
       <c r="L43" t="n">
-        <v>9.187251615830844e-05</v>
+        <v>0.0001727575336216</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4.957198748666829e-07</v>
+        <v>3.835797177861232e-05</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0019293228393244</v>
+        <v>0.0030251463997001</v>
       </c>
     </row>
     <row r="44">
@@ -3425,28 +3425,28 @@
         <v>12</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1151648507616269</v>
+        <v>-0.1495835170164518</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0538589585939114</v>
+        <v>0.0579720026194839</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0317299251587612</v>
+        <v>0.0093283821047876</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0336786582700349</v>
+        <v>0.0391864571479869</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2348217913652486</v>
+        <v>-0.2750988541690395</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0079302586790137</v>
+        <v>-0.0190546344218048</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0561605366336668</v>
+        <v>0.0598175103315673</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0638901387760331</v>
+        <v>0.0284973146830352</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.095189775476284</v>
+        <v>0.0559702926287257</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1916704163280992</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="45">
@@ -3480,28 +3480,28 @@
         <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3929110835570838</v>
+        <v>0.3763016744593977</v>
       </c>
       <c r="F45" t="n">
-        <v>0.09020988764907829</v>
+        <v>0.0871064196221772</v>
       </c>
       <c r="G45" t="n">
-        <v>4.164077652056255e-06</v>
+        <v>5.539959711509009e-06</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0962309916711339</v>
+        <v>0.0895295789921088</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1750855784643589</v>
+        <v>0.1597581302886113</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5740667337687348</v>
+        <v>0.5582931390845028</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1082831626709465</v>
+        <v>0.106591239427052</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0027715945817259</v>
+        <v>0.003424854025628</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>0.0001163391539416</v>
       </c>
       <c r="O45" t="n">
-        <v>0.0388023241441628</v>
+        <v>0.0719219345381894</v>
       </c>
     </row>
     <row r="46">
@@ -3535,28 +3535,28 @@
         <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.06882146358200419</v>
+        <v>-0.0866847381451003</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0810994713037526</v>
+        <v>0.07588751011069669</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3953533449187993</v>
+        <v>0.2521455879301491</v>
       </c>
       <c r="H46" t="n">
-        <v>0.07753766220356299</v>
+        <v>0.06762366128449911</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2293683540300579</v>
+        <v>-0.2396436969559079</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0953710436017205</v>
+        <v>0.07047335754050239</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0747811557113386</v>
+        <v>0.07155578490955911</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3764267939012534</v>
+        <v>0.2499939051233074</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.4412547788777609</v>
       </c>
       <c r="O46" t="n">
-        <v>0.6080740516866401</v>
+        <v>0.4772610915990415</v>
       </c>
     </row>
     <row r="47">
@@ -3590,28 +3590,28 @@
         <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>0.198551348376704</v>
+        <v>0.1777061972003546</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0871178299533064</v>
+        <v>0.0800608270566725</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0208997173073951</v>
+        <v>0.0248673100100703</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0897805310966085</v>
+        <v>0.075608645669036</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0271382819263582</v>
+        <v>0.0243784561306237</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3586214975978818</v>
+        <v>0.3228655859859993</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0790914232626358</v>
+        <v>0.0705274166448269</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0272755381448228</v>
+        <v>0.0271535402966346</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.0731490105758827</v>
+        <v>0.1044427020422956</v>
       </c>
       <c r="O47" t="n">
-        <v>0.12317056755548</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="48">
@@ -3645,28 +3645,28 @@
         <v>12</v>
       </c>
       <c r="E48" t="n">
-        <v>0.307570362511078</v>
+        <v>0.3013708976170193</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0911441789450937</v>
+        <v>0.0896696914248972</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0004876716148084</v>
+        <v>0.0005232108776439</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0983468561603915</v>
+        <v>0.09529039997741751</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1059728249759195</v>
+        <v>0.1053192621286071</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4848819004572947</v>
+        <v>0.4748720257839595</v>
       </c>
       <c r="K48" t="n">
-        <v>0.09608764086907411</v>
+        <v>0.09328344919946061</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0069780107742168</v>
+        <v>0.0066613422677565</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.0051205519554882</v>
+        <v>0.0073249522870149</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0732691131292771</v>
+        <v>0.093258791748592</v>
       </c>
     </row>
     <row r="49">
@@ -3700,28 +3700,28 @@
         <v>12</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.06971883135697921</v>
+        <v>-0.0961908586812482</v>
       </c>
       <c r="F49" t="n">
-        <v>0.08844742129727121</v>
+        <v>0.07665034538136919</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4298007800104128</v>
+        <v>0.2080943962574858</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0927256714816023</v>
+        <v>0.069318908994013</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2735778867342542</v>
+        <v>-0.2849722877272565</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1401345762216944</v>
+        <v>0.0997741119067785</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0958184417882593</v>
+        <v>0.0893219899095896</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4813550521416683</v>
+        <v>0.3031507187747018</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6983385602006522</v>
+        <v>0.5092932075414991</v>
       </c>
     </row>
     <row r="50">
@@ -3755,28 +3755,28 @@
         <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0195506708810455</v>
+        <v>0.00119727637589</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06552424812674359</v>
+        <v>0.066738184283054</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7653894247939892</v>
+        <v>0.9856867914105232</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0503765757503493</v>
+        <v>0.0523075963819621</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1575485223943052</v>
+        <v>-0.1865660736935026</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1954314563541592</v>
+        <v>0.1888762441250322</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0810659628960774</v>
+        <v>0.0863133066851572</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8138365706025813</v>
+        <v>0.9891810560940556</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0.8459567326670407</v>
+        <v>0.9856867914105232</v>
       </c>
       <c r="O50" t="n">
-        <v>0.899503578034432</v>
+        <v>0.9891810560940556</v>
       </c>
     </row>
     <row r="51">
@@ -3810,28 +3810,28 @@
         <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1849640157710767</v>
+        <v>0.2138968520196108</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1287844182087441</v>
+        <v>0.1241890063347173</v>
       </c>
       <c r="G51" t="n">
-        <v>0.146236794923678</v>
+        <v>0.0802285135523827</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1975452053115466</v>
+        <v>0.1833939559878451</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0723771465968316</v>
+        <v>-0.0194690900645684</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4192150631597932</v>
+        <v>0.4251605938190039</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1179570141577584</v>
+        <v>0.1075532213685508</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1409735719443923</v>
+        <v>0.0684228176025056</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0.2924735898473561</v>
+        <v>0.2246398379466714</v>
       </c>
       <c r="O51" t="n">
-        <v>0.31162579061392</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="52">
@@ -3865,28 +3865,28 @@
         <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>0.237988771978755</v>
+        <v>0.2472615001492901</v>
       </c>
       <c r="F52" t="n">
-        <v>0.08766647576759019</v>
+        <v>0.0798100765239991</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00564404721513</v>
+        <v>0.0015578579793562</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09063403079132309</v>
+        <v>0.0748535304581868</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0467253949362778</v>
+        <v>0.06646108480296339</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4124191206352126</v>
+        <v>0.4123410137395211</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0889972390557509</v>
+        <v>0.084477929495159</v>
       </c>
       <c r="L52" t="n">
-        <v>0.0197051471471153</v>
+        <v>0.012322479491112</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.0163575087832407</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1182308828826921</v>
+        <v>0.1035088277253409</v>
       </c>
     </row>
     <row r="53">
@@ -3920,28 +3920,28 @@
         <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1115901832647958</v>
+        <v>-0.076084640577745</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1210328209749718</v>
+        <v>0.1173640328854</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3545298430233478</v>
+        <v>0.515993070115634</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1744682053957214</v>
+        <v>0.1639918324461913</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3201977622615559</v>
+        <v>-0.2803421871981649</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1073386126689931</v>
+        <v>0.1347646232870103</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0998691809510307</v>
+        <v>0.0962393769821107</v>
       </c>
       <c r="L53" t="n">
-        <v>0.285742202609413</v>
+        <v>0.445044404527815</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.5956101362792237</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="O53" t="n">
-        <v>0.5404613258385168</v>
+        <v>0.6445470686264907</v>
       </c>
     </row>
     <row r="54">
@@ -3975,28 +3975,28 @@
         <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0748351353279772</v>
+        <v>-0.056427288262527</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1085654107604164</v>
+        <v>0.1029019080740663</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4898167527453207</v>
+        <v>0.5830445027974149</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1397979192784511</v>
+        <v>0.1255814805440221</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2929980822013008</v>
+        <v>-0.269937580400393</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1507347135379309</v>
+        <v>0.1623719458745877</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1030754120236772</v>
+        <v>0.1000957245183759</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4821861487099741</v>
+        <v>0.583851191958309</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.6857434538434487</v>
+        <v>0.7420566399239826</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6983385602006522</v>
+        <v>0.721227943007323</v>
       </c>
     </row>
     <row r="55">
@@ -4030,28 +4030,28 @@
         <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2529026805353643</v>
+        <v>0.2544122671804139</v>
       </c>
       <c r="F55" t="n">
-        <v>0.09185772501191811</v>
+        <v>0.0888225436324289</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0048889848069933</v>
+        <v>0.0034050328723985</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1000511999766322</v>
+        <v>0.0934976717148872</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0636789629623401</v>
+        <v>0.07265207622595279</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4245730551939283</v>
+        <v>0.4198165549449973</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0884813629928539</v>
+        <v>0.0851184746444318</v>
       </c>
       <c r="L55" t="n">
-        <v>0.0138964578738548</v>
+        <v>0.0109291231811725</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.0286022761281479</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1167302461403805</v>
+        <v>0.1035088277253409</v>
       </c>
     </row>
     <row r="56">
@@ -4085,28 +4085,28 @@
         <v>12</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0544765379594547</v>
+        <v>0.0617508833185083</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1006973094100091</v>
+        <v>0.0973314455139401</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5881429411141468</v>
+        <v>0.525267042630343</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1205797860467677</v>
+        <v>0.112568094487927</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1700488928910541</v>
+        <v>-0.1621072604206125</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2736250397220887</v>
+        <v>0.2795641211666401</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1027937579883137</v>
+        <v>0.1023994291446195</v>
       </c>
       <c r="L56" t="n">
-        <v>0.6063192855256394</v>
+        <v>0.5582179821043824</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7957940622524017</v>
+        <v>0.7104592499510322</v>
       </c>
     </row>
     <row r="57">
@@ -4140,28 +4140,28 @@
         <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0103493711456446</v>
+        <v>0.0287719352855015</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1060216946317194</v>
+        <v>0.0992884196711754</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9222347703388264</v>
+        <v>0.7719222861000943</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1333555854388239</v>
+        <v>0.1166963997484062</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2314594452101308</v>
+        <v>-0.1677366619802359</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2117774196000186</v>
+        <v>0.223081485904668</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1024001614555393</v>
+        <v>0.09001276767657369</v>
       </c>
       <c r="L57" t="n">
-        <v>0.921312416714388</v>
+        <v>0.7551626973103666</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.8313009234924091</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="58">
@@ -4195,28 +4195,28 @@
         <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1175212709036828</v>
+        <v>-0.1051210058351332</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07517767635821671</v>
+        <v>0.0714644436281691</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1162979164569188</v>
+        <v>0.1398339161408028</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0666137864614032</v>
+        <v>0.0600430148376677</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2782176337922586</v>
+        <v>-0.257719363051411</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0495747778755876</v>
+        <v>0.052593788583268</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0761851061588712</v>
+        <v>0.0718556261271559</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1494800774317796</v>
+        <v>0.1700095050055271</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0.2570796047995049</v>
+        <v>0.309106551469143</v>
       </c>
       <c r="O58" t="n">
-        <v>0.3139081626067374</v>
+        <v>0.3966888450128967</v>
       </c>
     </row>
     <row r="59">
@@ -4250,28 +4250,28 @@
         <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1189226781298659</v>
+        <v>0.1221020263878392</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1463367377005608</v>
+        <v>0.1333201150890139</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4141979595984009</v>
+        <v>0.357338373152656</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2557159038658096</v>
+        <v>0.2120194034789307</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.146375702143394</v>
+        <v>-0.1174695447840288</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3682620453869955</v>
+        <v>0.3482431262016101</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1212742695960595</v>
+        <v>0.109373160331783</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3456665183371182</v>
+        <v>0.2857658707820677</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.5604481202380235</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6049164070899569</v>
+        <v>0.5000902738686185</v>
       </c>
     </row>
     <row r="60">
@@ -4305,28 +4305,28 @@
         <v>12</v>
       </c>
       <c r="E60" t="n">
-        <v>0.30071423613326</v>
+        <v>0.3161392030475308</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1402012637788584</v>
+        <v>0.1314018955329955</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0268783421993116</v>
+        <v>0.0127303302216184</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2346274626807193</v>
+        <v>0.2059754023164602</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0059317748209497</v>
+        <v>0.0432340044537369</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5474113171350314</v>
+        <v>0.54514173422587</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1382893556998796</v>
+        <v>0.129074372276486</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0463848699476233</v>
+        <v>0.0276690099434119</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0.0868377209516225</v>
+        <v>0.0668342336634966</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1623470448166818</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="61">
@@ -4360,28 +4360,28 @@
         <v>12</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2141127051335998</v>
+        <v>-0.1824303123223145</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0851657774988611</v>
+        <v>0.0841277224473448</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0106621491592208</v>
+        <v>0.0283044453594218</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08597570365873659</v>
+        <v>0.08385747501520539</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3971406095562585</v>
+        <v>-0.3702521833187156</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.0147048441895512</v>
+        <v>0.0197217148961826</v>
       </c>
       <c r="K61" t="n">
-        <v>0.09212774640129739</v>
+        <v>0.0927856294329226</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0377731454265966</v>
+        <v>0.07222349668209239</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.0511106669488857</v>
+        <v>0.1080715186450653</v>
       </c>
       <c r="O61" t="n">
-        <v>0.1442247370833691</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="62">
@@ -4415,28 +4415,28 @@
         <v>12</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0604493384580512</v>
+        <v>-0.0445441632921047</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1303262190493734</v>
+        <v>0.1319149904383728</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6423632020527231</v>
+        <v>0.7354409218424243</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2026523232037846</v>
+        <v>0.2076528599658457</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3337714964441505</v>
+        <v>-0.3274170321043466</v>
       </c>
       <c r="J62" t="n">
-        <v>0.222248632874781</v>
+        <v>0.2456564964037124</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1301887354572371</v>
+        <v>0.1341938753120687</v>
       </c>
       <c r="L62" t="n">
-        <v>0.6510789227202867</v>
+        <v>0.7460126840175852</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8042739633603542</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="63">
@@ -4470,28 +4470,28 @@
         <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0813278196800928</v>
+        <v>-0.08675743075301259</v>
       </c>
       <c r="F63" t="n">
-        <v>0.086100422041967</v>
+        <v>0.0950749231238997</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3438119666013901</v>
+        <v>0.3602880772958722</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0877172814943448</v>
+        <v>0.1072045500373771</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2637961077095255</v>
+        <v>-0.2755127323890796</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1067599884169907</v>
+        <v>0.1084394131742403</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0857235366793182</v>
+        <v>0.08897996245913201</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3621188923366847</v>
+        <v>0.3493396730081546</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0.5956101362792237</v>
+        <v>0.5604481202380235</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6080740516866401</v>
+        <v>0.5434172691237962</v>
       </c>
     </row>
     <row r="64">
@@ -4525,28 +4525,28 @@
         <v>12</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.07418659164113819</v>
+        <v>-0.1189452752093276</v>
       </c>
       <c r="F64" t="n">
-        <v>0.070271556147551</v>
+        <v>0.07859568235614239</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2902122442822186</v>
+        <v>0.1283652433539746</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0578962376745405</v>
+        <v>0.07273046258168531</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2652293375292032</v>
+        <v>-0.3192658082047608</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1224611028140421</v>
+        <v>0.09155024284180339</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0896880124366502</v>
+        <v>0.0960107981901186</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4248985998669521</v>
+        <v>0.2390847525946817</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.5299527939066601</v>
+        <v>0.2995189011592744</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6609533775708145</v>
+        <v>0.4772610915990415</v>
       </c>
     </row>
     <row r="65">
@@ -4580,28 +4580,28 @@
         <v>12</v>
       </c>
       <c r="E65" t="n">
-        <v>0.197144370687171</v>
+        <v>0.1308074460592332</v>
       </c>
       <c r="F65" t="n">
-        <v>0.08316083233514029</v>
+        <v>0.1025211684129896</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0163017527327623</v>
+        <v>0.1994011729071937</v>
       </c>
       <c r="H65" t="n">
-        <v>0.08156685968913539</v>
+        <v>0.124720701072635</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0282373747741598</v>
+        <v>-0.0726038710278686</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3551060159787271</v>
+        <v>0.3237713448707424</v>
       </c>
       <c r="K65" t="n">
-        <v>0.07792638486071959</v>
+        <v>0.09281894168803539</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0263565621893862</v>
+        <v>0.1840643317975222</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.0622430558887288</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="O65" t="n">
-        <v>0.12317056755548</v>
+        <v>0.4068790492366281</v>
       </c>
     </row>
     <row r="66">
@@ -4635,28 +4635,28 @@
         <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1781078252134749</v>
+        <v>0.1488062659220301</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1061314848726169</v>
+        <v>0.1197005703401346</v>
       </c>
       <c r="G66" t="n">
-        <v>0.08983442692006589</v>
+        <v>0.2104045118731459</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1338887039092805</v>
+        <v>0.1706965281931942</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0558781627990554</v>
+        <v>-0.1047745806084774</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3935486380468497</v>
+        <v>0.384218511039829</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1072084781888367</v>
+        <v>0.1158935431407438</v>
       </c>
       <c r="L66" t="n">
-        <v>0.1212539140023427</v>
+        <v>0.2223084976231433</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0.2096136628134871</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2829257993387998</v>
+        <v>0.466847845008601</v>
       </c>
     </row>
     <row r="67">
@@ -4690,28 +4690,28 @@
         <v>12</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1013482235336964</v>
+        <v>-0.1311319480986029</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0521443350638274</v>
+        <v>0.0573218955960371</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0511397345538782</v>
+        <v>0.0213977967986999</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0314765218905181</v>
+        <v>0.0382619585950987</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2559360160344302</v>
+        <v>-0.2854903521424436</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0582937684291084</v>
+        <v>0.0298577737346122</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0727207583612476</v>
+        <v>0.0734934900076593</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1895288475214051</v>
+        <v>0.1002144346897993</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.1342418032039302</v>
+        <v>0.09985638506059991</v>
       </c>
       <c r="O67" t="n">
-        <v>0.3790576950428103</v>
+        <v>0.2630628910607233</v>
       </c>
     </row>
     <row r="68">
@@ -4745,28 +4745,28 @@
         <v>12</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0943597987805897</v>
+        <v>-0.090652549266062</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0811683367949108</v>
+        <v>0.0856595952560132</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2436190457284472</v>
+        <v>0.2885982635550075</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0780323886663907</v>
+        <v>0.0870154240223359</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2770479794516279</v>
+        <v>-0.2830323578553245</v>
       </c>
       <c r="J68" t="n">
-        <v>0.09491251685489741</v>
+        <v>0.1087395712273311</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0862524794640053</v>
+        <v>0.090901718006276</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2959669165306163</v>
+        <v>0.3387987262017397</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.4650909054815812</v>
+        <v>0.4848450827724126</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5404613258385168</v>
+        <v>0.5434172691237962</v>
       </c>
     </row>
     <row r="69">
@@ -4800,28 +4800,28 @@
         <v>12</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0073171606767699</v>
+        <v>0.014080908184194</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0696660076289294</v>
+        <v>0.0695300580309257</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9163489229430256</v>
+        <v>0.8395033491805962</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0570535258731849</v>
+        <v>0.0567401745277588</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1323258977564313</v>
+        <v>-0.1000354527578815</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1179207010727951</v>
+        <v>0.127831633195756</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0571513041028023</v>
+        <v>0.0520008038729924</v>
       </c>
       <c r="L69" t="n">
-        <v>0.9004330718650579</v>
+        <v>0.7915585292743212</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.881478516639626</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="70">
@@ -4855,28 +4855,28 @@
         <v>12</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0202499400312667</v>
+        <v>0.014761791539591</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0420754057371667</v>
+        <v>0.0453081494556145</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6302726294542583</v>
+        <v>0.7445511493957188</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0201915627397792</v>
+        <v>0.023543436248837</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1156346909467774</v>
+        <v>-0.1258305264253189</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1553905451008432</v>
+        <v>0.1547728265755853</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0619754169289396</v>
+        <v>0.0641821122678102</v>
       </c>
       <c r="L70" t="n">
-        <v>0.7499633608676821</v>
+        <v>0.8223013517487056</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8513097609849364</v>
+        <v>0.8634164193361409</v>
       </c>
     </row>
     <row r="71">
@@ -4910,28 +4910,28 @@
         <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1148190340461117</v>
+        <v>0.1027416275850512</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0635356044379331</v>
+        <v>0.0633714131724113</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0694984923580811</v>
+        <v>0.1037365833335193</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0472531879979727</v>
+        <v>0.046955165086824</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0260568978964209</v>
+        <v>-0.0325770564339839</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2512232716746054</v>
+        <v>0.2343614820400233</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0642396105536738</v>
+        <v>0.0616514973685831</v>
       </c>
       <c r="L71" t="n">
-        <v>0.1001020899164612</v>
+        <v>0.1226173555133485</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.1717021575905537</v>
+        <v>0.2562903823534009</v>
       </c>
       <c r="O71" t="n">
-        <v>0.2473110456759631</v>
+        <v>0.3029369959741552</v>
       </c>
     </row>
     <row r="72">
@@ -4965,28 +4965,28 @@
         <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1415445330117672</v>
+        <v>0.1445519287970761</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0692205629062527</v>
+        <v>0.0721061773213143</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0395271918256784</v>
+        <v>0.0435028072635916</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0563812795713198</v>
+        <v>0.0612635815617653</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0128619453640578</v>
+        <v>-0.0148979929589236</v>
       </c>
       <c r="J72" t="n">
-        <v>0.2893578813832472</v>
+        <v>0.2968322836104786</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0705883862778367</v>
+        <v>0.0729085583413055</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0685615261545842</v>
+        <v>0.0712136268181225</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.1106761371118995</v>
+        <v>0.1522598254225705</v>
       </c>
       <c r="O72" t="n">
-        <v>0.1919722732328358</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="73">
@@ -5020,28 +5020,28 @@
         <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.0282755987117917</v>
+        <v>-0.0234653123438686</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0614785239901134</v>
+        <v>0.0640542948112756</v>
       </c>
       <c r="G73" t="n">
-        <v>0.6454809984885215</v>
+        <v>0.7140651407261371</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0443188167818873</v>
+        <v>0.0481828348038295</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2111674204251198</v>
+        <v>-0.2079877455667061</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1565291419097307</v>
+        <v>0.162669893826652</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0845574994339051</v>
+        <v>0.085233452544037</v>
       </c>
       <c r="L73" t="n">
-        <v>0.7443050453896075</v>
+        <v>0.7881457411294868</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="O73" t="n">
-        <v>0.8513097609849364</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="74">
@@ -5075,28 +5075,28 @@
         <v>12</v>
       </c>
       <c r="E74" t="n">
-        <v>0.08228956127094771</v>
+        <v>0.0143033693267382</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0335745792877448</v>
+        <v>0.0411759603530726</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0140296536688216</v>
+        <v>0.7282941855402352</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0125350946703402</v>
+        <v>0.0193415355790013</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.005578057052981</v>
+        <v>-0.0794989003763466</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1688962069234841</v>
+        <v>0.1078545545612246</v>
       </c>
       <c r="K74" t="n">
-        <v>0.040006711237899</v>
+        <v>0.0426951369770293</v>
       </c>
       <c r="L74" t="n">
-        <v>0.06369426638648951</v>
+        <v>0.7439010472413939</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.0589245454090507</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="O74" t="n">
-        <v>0.1916704163280992</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="75">
@@ -5130,28 +5130,28 @@
         <v>12</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.0282541570309344</v>
+        <v>-0.0466740056492061</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0653727369693184</v>
+        <v>0.0706293264370926</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6655117723040752</v>
+        <v>0.5084129607162668</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0501287184964532</v>
+        <v>0.0586856060172838</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1734822393531533</v>
+        <v>-0.200321535569624</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1181765830151451</v>
+        <v>0.1092142629602496</v>
       </c>
       <c r="K75" t="n">
-        <v>0.066785120055426</v>
+        <v>0.07104071834624009</v>
       </c>
       <c r="L75" t="n">
-        <v>0.6803238824383578</v>
+        <v>0.5243907429939032</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="O75" t="n">
-        <v>0.8163886589260294</v>
+        <v>0.688262850179498</v>
       </c>
     </row>
     <row r="76">
@@ -5185,28 +5185,28 @@
         <v>12</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.009526118292628</v>
+        <v>-0.0453533491836163</v>
       </c>
       <c r="F76" t="n">
-        <v>0.09681788300942359</v>
+        <v>0.09534095216096281</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9216185557311652</v>
+        <v>0.6340580092904678</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1113961841305103</v>
+        <v>0.1079876137471633</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1539904885406871</v>
+        <v>-0.1880623984362696</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1353370049628998</v>
+        <v>0.09923115597058479</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0661971272732563</v>
+        <v>0.0658538204450142</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8881744029495801</v>
+        <v>0.5049936055797279</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.783248129123519</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.6841848849789862</v>
       </c>
     </row>
     <row r="77">
@@ -5240,28 +5240,28 @@
         <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0386160199952164</v>
+        <v>-0.0391812806053732</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0635251340605936</v>
+        <v>0.061298231059251</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5430627126520327</v>
+        <v>0.5224857215542513</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0473341801294636</v>
+        <v>0.043985258276366</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1743392570575623</v>
+        <v>-0.1614134449139473</v>
       </c>
       <c r="J77" t="n">
-        <v>0.09854713346925741</v>
+        <v>0.084234833317861</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0624735025216925</v>
+        <v>0.0561731477290869</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5488859160221319</v>
+        <v>0.499746744487911</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0.7357623848833993</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7436518862235335</v>
+        <v>0.6841848849789862</v>
       </c>
     </row>
     <row r="78">
@@ -5295,28 +5295,28 @@
         <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0297111967575133</v>
+        <v>-0.0509332931107738</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0662002095495702</v>
+        <v>0.06786385243080779</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6534747014039251</v>
+        <v>0.4525493284045447</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0514316348811398</v>
+        <v>0.0540818867317153</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1683025697481732</v>
+        <v>-0.1830908363855966</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1100320388347824</v>
+        <v>0.0830324464200652</v>
       </c>
       <c r="K78" t="n">
-        <v>0.06369842635156529</v>
+        <v>0.0609733617942703</v>
       </c>
       <c r="L78" t="n">
-        <v>0.6499099271436581</v>
+        <v>0.4209113296888605</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.6788239926068171</v>
       </c>
       <c r="O78" t="n">
-        <v>0.8042739633603542</v>
+        <v>0.6313669945332908</v>
       </c>
     </row>
     <row r="79">
@@ -5350,28 +5350,28 @@
         <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.1095332919108243</v>
+        <v>-0.1153443197184127</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07378127040326291</v>
+        <v>0.0691593398483866</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1360802379605801</v>
+        <v>0.0938829685636088</v>
       </c>
       <c r="H79" t="n">
-        <v>0.06425535201204351</v>
+        <v>0.0563272300676558</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2374055807680123</v>
+        <v>-0.2375832778121036</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0220703156418786</v>
+        <v>0.0104909302612169</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0599951414658069</v>
+        <v>0.0574066946423871</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0939731439968992</v>
+        <v>0.0686243716980988</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.2857684997172183</v>
+        <v>0.2464427924794729</v>
       </c>
       <c r="O79" t="n">
-        <v>0.2466795029918604</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="80">
@@ -5405,28 +5405,28 @@
         <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1875950862962451</v>
+        <v>0.1484444053590013</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0746175836730119</v>
+        <v>0.0835541276760129</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0109522857747612</v>
+        <v>0.07347791743154761</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0656582308694361</v>
+        <v>0.0826369274190968</v>
       </c>
       <c r="I80" t="n">
-        <v>0.022932261626653</v>
+        <v>-0.0141225357771847</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3423485325978941</v>
+        <v>0.3033657002568551</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0758328969432773</v>
+        <v>0.07436346731068399</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0293263256084476</v>
+        <v>0.06947406302122899</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.0511106669488857</v>
+        <v>0.220433752294643</v>
       </c>
       <c r="O80" t="n">
-        <v>0.12317056755548</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="81">
@@ -5460,28 +5460,28 @@
         <v>12</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3693497064662411</v>
+        <v>0.3095342042068454</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0860395926342943</v>
+        <v>0.0579258612111506</v>
       </c>
       <c r="G81" t="n">
-        <v>6.614986964351846e-06</v>
+        <v>3.298165340588464e-08</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0877228530571315</v>
+        <v>0.0391815597356643</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1911859475239888</v>
+        <v>0.1828331208641323</v>
       </c>
       <c r="J81" t="n">
-        <v>0.5239521045095376</v>
+        <v>0.4261215566341095</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0881887131764762</v>
+        <v>0.0613897574402089</v>
       </c>
       <c r="L81" t="n">
-        <v>0.0010704368423174</v>
+        <v>0.0002885743667336</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>1.38522944304715e-06</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0265458223516252</v>
+        <v>0.0121201234028134</v>
       </c>
     </row>
     <row r="82">
@@ -5515,28 +5515,28 @@
         <v>12</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0378506864581246</v>
+        <v>-0.0030801467779988</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0482368773247829</v>
+        <v>0.0545049191414286</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4324191807107754</v>
+        <v>0.9549343084645984</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0267656504927931</v>
+        <v>0.0345761200119597</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0874799725373249</v>
+        <v>-0.116540835268485</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1620017470883768</v>
+        <v>0.1104599014124427</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0570530583308012</v>
+        <v>0.0517916397750246</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5205212951540538</v>
+        <v>0.953642806643027</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.9782253891588568</v>
       </c>
       <c r="O82" t="n">
-        <v>0.7287298132156752</v>
+        <v>0.9769023872928568</v>
       </c>
     </row>
     <row r="83">
@@ -5570,28 +5570,28 @@
         <v>12</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2298677784709847</v>
+        <v>0.1415609904301918</v>
       </c>
       <c r="F83" t="n">
-        <v>0.051976128332198</v>
+        <v>0.0536865176330512</v>
       </c>
       <c r="G83" t="n">
-        <v>6.699264022849131e-06</v>
+        <v>0.007939417100162299</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0312433935269703</v>
+        <v>0.033415018548571</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1136491736917842</v>
+        <v>0.0293405063954434</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3398805089075868</v>
+        <v>0.2502573427532493</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0544790410413693</v>
+        <v>0.0514175205754164</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0012640867786488</v>
+        <v>0.0181690134316627</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>0.0555759197011362</v>
       </c>
       <c r="O83" t="n">
-        <v>0.0265458223516252</v>
+        <v>0.1271830940216392</v>
       </c>
     </row>
     <row r="84">
@@ -5625,28 +5625,28 @@
         <v>12</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2351137202622659</v>
+        <v>0.1532743291694626</v>
       </c>
       <c r="F84" t="n">
-        <v>0.08514136044392399</v>
+        <v>0.0803353448564879</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0048915303337827</v>
+        <v>0.0544691677930575</v>
       </c>
       <c r="H84" t="n">
-        <v>0.08563346970936241</v>
+        <v>0.0760843313335707</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0512762977547417</v>
+        <v>-0.0075413933126175</v>
       </c>
       <c r="J84" t="n">
-        <v>0.403539574535314</v>
+        <v>0.3063616142247047</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0855409085277743</v>
+        <v>0.0736185636244205</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0172455218594035</v>
+        <v>0.0597506894792608</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.1759773113314167</v>
       </c>
       <c r="O84" t="n">
-        <v>0.1182308828826921</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="85">
@@ -5680,28 +5680,28 @@
         <v>12</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0041910196860204</v>
+        <v>-0.0605492687065162</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0610048575136991</v>
+        <v>0.0528366226486081</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9452282810295732</v>
+        <v>0.2512266101949149</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0435594724922558</v>
+        <v>0.0324166851844483</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1474986497676353</v>
+        <v>-0.177071424664924</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1556880619964321</v>
+        <v>0.0576468499150623</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0694114313542015</v>
+        <v>0.053764225070954</v>
       </c>
       <c r="L85" t="n">
-        <v>0.9529362347228644</v>
+        <v>0.2834924967314138</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0.9452282810295736</v>
+        <v>0.4412547788777609</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9529362347228644</v>
+        <v>0.5000902738686185</v>
       </c>
     </row>
   </sheetData>
@@ -5773,16 +5773,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1743730792512082</v>
+        <v>0.1477957457335625</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3693497064662411</v>
+        <v>0.3095342042068454</v>
       </c>
       <c r="E2" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>1.38522944304715e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0265458223516252</v>
+        <v>0.0121201234028134</v>
       </c>
     </row>
     <row r="3">
@@ -5797,46 +5797,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1021127468090447</v>
+        <v>0.1469946711409901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.197144370687171</v>
+        <v>0.1308074460592332</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0622430558887288</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.12317056755548</v>
+        <v>0.4068790492366281</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>malignant_OC_like</t>
+          <t>malignant_AC_like</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>astrocyte</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0221069999577731</v>
+        <v>0.08971109386532861</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1189226781298659</v>
+        <v>0.3763016744593977</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.0001163391539416</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6049164070899569</v>
+        <v>0.0719219345381894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>malignant_AC_like</t>
+          <t>malignant_OC_like</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5845,88 +5845,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.010618405846497</v>
+        <v>0.0516773360882904</v>
       </c>
       <c r="D5" t="n">
-        <v>0.198551348376704</v>
+        <v>0.1221020263878392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0731490105758827</v>
+        <v>0.5604481202380235</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12317056755548</v>
+        <v>0.5000902738686185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_hypoxia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>astrocyte</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.0228585381563033</v>
+        <v>0.0507626869999035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1148190340461117</v>
+        <v>-0.0466740056492061</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1717021575905537</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2473110456759631</v>
+        <v>0.688262850179498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>malignant_AC_like</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>astrocyte</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.0508939027286581</v>
+        <v>0.0202924010452081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3929110835570838</v>
+        <v>0.1027416275850512</v>
       </c>
       <c r="E7" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>0.2562903823534009</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0388023241441628</v>
+        <v>0.3029369959741552</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>malignant_MES_like</t>
+          <t>malignant_AC_like</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>astrocyte</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.0754065514433807</v>
+        <v>0.001556545583634</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1849640157710767</v>
+        <v>0.1777061972003546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2924735898473561</v>
+        <v>0.1044427020422956</v>
       </c>
       <c r="F8" t="n">
-        <v>0.31162579061392</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="9">
@@ -5937,68 +5937,68 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>astrocyte</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.1194178448521983</v>
+        <v>-0.0557748758576386</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1115901832647958</v>
+        <v>0.2138968520196108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5956101362792237</v>
+        <v>0.2246398379466714</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5404613258385168</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>malignant_novel_MP9</t>
+          <t>malignant_hypoxia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>T_NK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.14609095656306</v>
+        <v>-0.07098556517648499</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2298677784709847</v>
+        <v>0.0143033693267382</v>
       </c>
       <c r="E10" t="n">
-        <v>9.378969631988784e-05</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0265458223516252</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>malignant_hypoxia</t>
+          <t>malignant_MES_like</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>astrocyte</t>
+          <t>vascular</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.1521329899762761</v>
+        <v>-0.1167138181982362</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0282541570309344</v>
+        <v>0.2544122671804139</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.0286022761281479</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8163886589260294</v>
+        <v>0.1035088277253409</v>
       </c>
     </row>
     <row r="12">
@@ -6009,20 +6009,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vascular</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.1785664877652851</v>
+        <v>-0.1187725820001893</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2529026805353643</v>
+        <v>-0.076084640577745</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1167302461403805</v>
+        <v>0.6445470686264907</v>
       </c>
     </row>
     <row r="13">
@@ -6033,20 +6033,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T_NK</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.1987838432602403</v>
+        <v>-0.1419657806642115</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1875950862962451</v>
+        <v>0.1415609904301918</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0511106669488857</v>
+        <v>0.0555759197011362</v>
       </c>
       <c r="F13" t="n">
-        <v>0.12317056755548</v>
+        <v>0.1271830940216392</v>
       </c>
     </row>
     <row r="14">
@@ -6057,98 +6057,98 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neuron</t>
+          <t>vascular</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.2208258002606656</v>
+        <v>-0.1802921120752549</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0386160199952164</v>
+        <v>-0.1153443197184127</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7357623848833993</v>
+        <v>0.2464427924794729</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7436518862235335</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>malignant_hypoxia</t>
+          <t>malignant_OC_like</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T_NK</t>
+          <t>oligodendrocyte</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.2443028892908736</v>
+        <v>-0.1967659458233515</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08228956127094771</v>
+        <v>0.3161392030475308</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0589245454090507</v>
+        <v>0.0668342336634966</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1916704163280992</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_hypoxia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vascular</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.2481360236200631</v>
+        <v>-0.2072618130589403</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0282755987117917</v>
+        <v>-0.0453533491836163</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.783248129123519</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8513097609849364</v>
+        <v>0.6841848849789862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>malignant_OC_like</t>
+          <t>malignant_novel_MP9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>oligodendrocyte</t>
+          <t>T_NK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.2620523060814309</v>
+        <v>-0.211449824837832</v>
       </c>
       <c r="D17" t="n">
-        <v>0.30071423613326</v>
+        <v>0.1484444053590013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0868377209516225</v>
+        <v>0.220433752294643</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1623470448166818</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>malignant_novel_MP9</t>
+          <t>malignant_hypoxia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6157,22 +6157,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.272534470541903</v>
+        <v>-0.2280881594185368</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2351137202622659</v>
+        <v>-0.0509332931107738</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.6788239926068171</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1182308828826921</v>
+        <v>0.6313669945332908</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>malignant_AC_like</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6181,16 +6181,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.2799431224257957</v>
+        <v>-0.2483300826619863</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06971883135697921</v>
+        <v>-0.0234653123438686</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6983385602006522</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="20">
@@ -6201,26 +6201,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vascular</t>
+          <t>neuron</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.2950408949266228</v>
+        <v>-0.2506272274195816</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1095332919108243</v>
+        <v>-0.0391812806053732</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2857684997172183</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2466795029918604</v>
+        <v>0.6841848849789862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_novel_MP9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6229,46 +6229,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.3023294350891342</v>
+        <v>-0.2506539951857497</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1415445330117672</v>
+        <v>0.1532743291694626</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1106761371118995</v>
+        <v>0.1759773113314167</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1919722732328358</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>malignant_hypoxia</t>
+          <t>malignant_novel_MP9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>oligodendrocyte</t>
+          <t>vascular</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.3366238495631799</v>
+        <v>-0.2597501266062371</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0297111967575133</v>
+        <v>-0.0605492687065162</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.4412547788777609</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8042739633603542</v>
+        <v>0.5000902738686185</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>malignant_OPC_like</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6277,16 +6277,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.3513270805790028</v>
+        <v>-0.2903211420173724</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1781078252134749</v>
+        <v>0.1445519287970761</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2096136628134871</v>
+        <v>0.1522598254225705</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2829257993387998</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="24">
@@ -6297,26 +6297,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oligodendrocyte</t>
+          <t>vascular</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.3568388449739249</v>
+        <v>-0.2905917549946107</v>
       </c>
       <c r="D24" t="n">
-        <v>0.307570362511078</v>
+        <v>-0.0961908586812482</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0051205519554882</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0732691131292771</v>
+        <v>0.5092932075414991</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>malignant_MES_like</t>
+          <t>malignant_OPC_like</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6325,64 +6325,64 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.361076486984598</v>
+        <v>-0.2977582755615625</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0748351353279772</v>
+        <v>0.1488062659220301</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6857434538434487</v>
+        <v>0.4016813408487329</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6983385602006522</v>
+        <v>0.466847845008601</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>malignant_hypoxia</t>
+          <t>malignant_AC_like</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>oligodendrocyte</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.367583926754697</v>
+        <v>-0.3079005086510469</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.009526118292628</v>
+        <v>0.3013708976170193</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.0073249522870149</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.093258791748592</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_MES_like</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T_NK</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.3752307096685942</v>
+        <v>-0.3176804251745335</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0943597987805897</v>
+        <v>0.2472615001492901</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4650909054815812</v>
+        <v>0.0163575087832407</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5404613258385168</v>
+        <v>0.1035088277253409</v>
       </c>
     </row>
     <row r="28">
@@ -6393,26 +6393,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>oligodendrocyte</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.3835159163918074</v>
+        <v>-0.3268558934031356</v>
       </c>
       <c r="D28" t="n">
-        <v>0.237988771978755</v>
+        <v>-0.056427288262527</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0338642832907802</v>
+        <v>0.7420566399239826</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1182308828826921</v>
+        <v>0.721227943007323</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_novel_MP9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.3839115189640725</v>
+        <v>-0.3598538800461453</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0202499400312667</v>
+        <v>-0.0030801467779988</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.9782253891588568</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8513097609849364</v>
+        <v>0.9769023872928568</v>
       </c>
     </row>
     <row r="30">
@@ -6445,46 +6445,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.3907519029828951</v>
+        <v>-0.3693331854288416</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2141127051335998</v>
+        <v>-0.1824303123223145</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0511106669488857</v>
+        <v>0.1080715186450653</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1442247370833691</v>
+        <v>0.2022257907098587</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>malignant_OPC_like</t>
+          <t>malignant_MES_like</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vascular</t>
+          <t>T_NK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.4101153456959233</v>
+        <v>-0.3781420012018435</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1013482235336964</v>
+        <v>0.00119727637589</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1342418032039302</v>
+        <v>0.9856867914105232</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3790576950428103</v>
+        <v>0.9891810560940556</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>malignant_MES_like</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6493,112 +6493,112 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.443055243415099</v>
+        <v>-0.3785446013715443</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0195506708810455</v>
+        <v>-0.090652549266062</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8459567326670407</v>
+        <v>0.4848450827724126</v>
       </c>
       <c r="F32" t="n">
-        <v>0.899503578034432</v>
+        <v>0.5434172691237962</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>malignant_novel_MP9</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vascular</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.4432250238064293</v>
+        <v>-0.3872717670296718</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0041910196860204</v>
+        <v>0.014761791539591</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9452282810295736</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9529362347228644</v>
+        <v>0.8634164193361409</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>malignant_novel_MP9</t>
+          <t>malignant_OPC_like</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>vascular</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.4537744641279856</v>
+        <v>-0.4078346489605303</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0378506864581246</v>
+        <v>-0.1311319480986029</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.09985638506059991</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7287298132156752</v>
+        <v>0.2630628910607233</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>malignant_OC_like</t>
+          <t>malignant_AC_like</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>T_NK</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.4944795664320087</v>
+        <v>-0.4417415085262538</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1175212709036828</v>
+        <v>-0.1495835170164518</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2570796047995049</v>
+        <v>0.0559702926287257</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3139081626067374</v>
+        <v>0.1329874685208311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>malignant_AC_like</t>
+          <t>malignant_OC_like</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>T_NK</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.5004961417061252</v>
+        <v>-0.4493207010321429</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.06882146358200419</v>
+        <v>0.0617508833185083</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6262622617190534</v>
+        <v>0.6894129934523254</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6080740516866401</v>
+        <v>0.7104592499510322</v>
       </c>
     </row>
     <row r="37">
@@ -6609,26 +6609,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T_NK</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.5033395953415022</v>
+        <v>-0.450552873065593</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0544765379594547</v>
+        <v>-0.1051210058351332</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.309106551469143</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7957940622524017</v>
+        <v>0.3966888450128967</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>malignant_OPC_like</t>
+          <t>malignant_AC_like</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6637,22 +6637,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.5419412400464163</v>
+        <v>-0.4508402542678773</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.07418659164113819</v>
+        <v>-0.0866847381451003</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5299527939066601</v>
+        <v>0.4412547788777609</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6609533775708145</v>
+        <v>0.4772610915990415</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>malignant_AC_like</t>
+          <t>malignant_OPC_like</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6661,64 +6661,64 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.5427335627649449</v>
+        <v>-0.5026951639233046</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1151648507616269</v>
+        <v>-0.0445441632921047</v>
       </c>
       <c r="E39" t="n">
-        <v>0.095189775476284</v>
+        <v>0.8229249545952683</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1916704163280992</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>malignant_cycling</t>
+          <t>malignant_OPC_like</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>astrocyte</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.5462290824782026</v>
+        <v>-0.5036589082864932</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0073171606767699</v>
+        <v>-0.1189452752093276</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.2995189011592744</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.4772610915990415</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>malignant_OPC_like</t>
+          <t>malignant_cycling</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T_NK</t>
+          <t>astrocyte</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.5689862816011315</v>
+        <v>-0.5484967782291308</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0604493384580512</v>
+        <v>0.014080908184194</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7554457955884095</v>
+        <v>0.881478516639626</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8042739633603542</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="42">
@@ -6733,16 +6733,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.6302115049999037</v>
+        <v>-0.5826121149029267</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0103493711456446</v>
+        <v>0.0287719352855015</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9447283013227002</v>
+        <v>0.8313009234924091</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9437834512683974</v>
+        <v>0.8524476469108074</v>
       </c>
     </row>
     <row r="43">
@@ -6757,16 +6757,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.6658091028711827</v>
+        <v>-0.6112672566369242</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0813278196800928</v>
+        <v>-0.08675743075301259</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5956101362792237</v>
+        <v>0.5604481202380235</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6080740516866401</v>
+        <v>0.5434172691237962</v>
       </c>
     </row>
   </sheetData>
